--- a/app/static/storage/June 2026 - MRC .xlsx
+++ b/app/static/storage/June 2026 - MRC .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B510C4A-178D-47E0-8148-DC4A4B9C0234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAF1471-D808-42C5-AF6E-EA21E73DA36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{04BD68B6-BA57-E345-845D-456FEAAF2C03}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Civil Case 2026" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="88">
   <si>
     <t>June 2026</t>
   </si>
@@ -915,7 +915,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1347962</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>263402</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="356" cy="356"/>
@@ -941,6 +941,49 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6199362" y="6397502"/>
+          <a:ext cx="356" cy="356"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln cap="flat">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1347962</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>263402</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="356" cy="356"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Ink 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33FB025A-FCAF-4762-9BE8-F9726B251E03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6205712" y="6759452"/>
           <a:ext cx="356" cy="356"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2202,152 +2245,158 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="71" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="73"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
-        <v>1</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="18">
-        <v>46161</v>
+    <row r="15" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>2</v>
+      </c>
+      <c r="B15" s="51">
+        <v>744</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="54">
+        <v>45216</v>
+      </c>
+      <c r="F15" s="44">
+        <v>15</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>3</v>
+      </c>
+      <c r="B16" s="55">
+        <v>754</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="54">
+        <v>45531</v>
       </c>
       <c r="F16" s="44">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="73"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>1</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="18">
+        <v>46161</v>
+      </c>
+      <c r="F18" s="44">
+        <v>12</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
         <v>2</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E19" s="18">
         <v>46167</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F19" s="44">
         <v>12</v>
       </c>
-      <c r="G17" s="45" t="s">
+      <c r="G19" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="21"/>
-    </row>
-    <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6" t="s">
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F22" s="16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="69" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="70"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-    </row>
-    <row r="22" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>1</v>
-      </c>
-      <c r="B22" s="51">
-        <v>744</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="54">
-        <v>45216</v>
-      </c>
-      <c r="F22" s="44">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="57.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>2</v>
-      </c>
-      <c r="B23" s="55">
-        <v>754</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="54">
-        <v>45531</v>
-      </c>
-      <c r="F23" s="44">
-        <v>15</v>
-      </c>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
     </row>
     <row r="24" spans="1:7" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="55">
         <v>758</v>
@@ -2367,7 +2416,7 @@
     </row>
     <row r="25" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A25" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B25" s="11">
         <v>761</v>
@@ -2387,7 +2436,7 @@
     </row>
     <row r="26" spans="1:7" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B26" s="11">
         <v>764</v>
@@ -2407,7 +2456,7 @@
     </row>
     <row r="27" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A27" s="12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" s="58">
         <v>766</v>
@@ -2427,7 +2476,7 @@
     </row>
     <row r="28" spans="1:7" ht="57.75" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28" s="58">
         <v>767</v>
@@ -2447,7 +2496,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B29" s="11">
         <v>768</v>
@@ -2466,8 +2515,8 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="62">
-        <v>9</v>
+      <c r="A30" s="12">
+        <v>7</v>
       </c>
       <c r="B30" s="12">
         <v>769</v>
@@ -2607,12 +2656,12 @@
   <mergeCells count="11">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A10:F10"/>
